--- a/src/main/resources/sql/20260819/app层/数据映射细化V4.xlsx
+++ b/src/main/resources/sql/20260819/app层/数据映射细化V4.xlsx
@@ -3052,17 +3052,15 @@
 FROM app_customer_info c
 WHERE c.reportNo = #{reportNo}
   AND c.customerId = #{customerId};
--- 2) 股东及持股比例（最新快照，按比例倒序）
+-- 2) 股东及持股比例（信贷系统股东最新，按比例倒序）
 SELECT
-    s.name           AS 股东名称,
-    s.stock_num      AS 持股数,
-    s.amount         AS 应出资金额,
-    s.stock_percent  AS 持股比例,
-    s.is_state_owned AS 是否国资股东
-FROM app_shareholder_info s
-WHERE a.reportNo = #{reportNo}
-  AND a.customerId = #{customerId}
-ORDER BY s.stock_percent DESC;
+    x.name           AS 股东名称,
+    x.oughtSum       AS 应出资金额,
+    x.investmentProp AS 持股比例
+FROM app_xd_shareholder_info x
+WHERE x.reportNo = #{reportNo}
+  AND x.customerId = #{customerId}
+ORDER BY x.investmentProp DESC;
 -- 3) 实际控制人（系统口径）
 SELECT
     c.actualController AS 实际控制人
@@ -3490,7 +3488,7 @@
       <c r="N19" s="215" t="n"/>
       <c r="O19" s="216" t="inlineStr">
         <is>
-          <t>app_shareholder_info</t>
+          <t>app_xd_shareholder_info</t>
         </is>
       </c>
       <c r="P19" s="216" t="inlineStr">
@@ -3537,12 +3535,12 @@
       <c r="N20" s="215" t="n"/>
       <c r="O20" s="216" t="inlineStr">
         <is>
-          <t>app_shareholder_info</t>
+          <t>app_xd_shareholder_info</t>
         </is>
       </c>
       <c r="P20" s="216" t="inlineStr">
         <is>
-          <t>stock_percent</t>
+          <t>investmentProp</t>
         </is>
       </c>
       <c r="Q20" s="217" t="inlineStr"/>
@@ -3584,12 +3582,12 @@
       <c r="N21" s="215" t="n"/>
       <c r="O21" s="216" t="inlineStr">
         <is>
-          <t>app_shareholder_info</t>
+          <t>app_xd_shareholder_info</t>
         </is>
       </c>
       <c r="P21" s="216" t="inlineStr">
         <is>
-          <t>amount</t>
+          <t>oughtSum</t>
         </is>
       </c>
       <c r="Q21" s="217" t="inlineStr"/>
@@ -3872,12 +3870,12 @@
       </c>
       <c r="O25" s="164" t="inlineStr">
         <is>
-          <t>app_early_warning_info</t>
+          <t>app_early_warning_signal_info</t>
         </is>
       </c>
       <c r="P25" s="164" t="inlineStr">
         <is>
-          <t>warningNo</t>
+          <t>serialNo</t>
         </is>
       </c>
       <c r="Q25" s="165" t="inlineStr">
@@ -3885,14 +3883,14 @@
           <t>-- 经验库规则判断所需源数据（二、客户基本情况，规则引擎自行判断命中逻辑）
 【1】提供数据：预警编号、风险原因、信号状态、预警信号风险等级、信号建立时间
     时点：当前最新（表无快照）
--- 源数据表：app_early_warning_info
+-- 源数据表：app_early_warning_signal_info
 SELECT
-    a.warningNo AS 预警编号,
-    a.riskReason AS 风险原因,
-    a.signalStatus AS 信号状态,
-    a.signalRiskLevel AS 预警信号风险等级,
-    a.signalCreateTime AS 信号建立时间
-FROM app_early_warning_info a
+    a.serialNo AS 预警编号,
+    a.riskMessage AS 风险原因,
+    a.status AS 信号状态,
+    a.warningLevel AS 预警信号风险等级,
+    a.inputDate AS 信号建立时间
+FROM app_early_warning_signal_info a
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId};</t>
         </is>
@@ -3939,12 +3937,12 @@
       </c>
       <c r="O26" s="243" t="inlineStr">
         <is>
-          <t>app_early_warning_info</t>
+          <t>app_early_warning_signal_info</t>
         </is>
       </c>
       <c r="P26" s="243" t="inlineStr">
         <is>
-          <t>riskReason</t>
+          <t>riskMessage</t>
         </is>
       </c>
       <c r="Q26" s="244" t="inlineStr"/>
@@ -3990,12 +3988,12 @@
       </c>
       <c r="O27" s="243" t="inlineStr">
         <is>
-          <t>app_early_warning_info</t>
+          <t>app_early_warning_signal_info</t>
         </is>
       </c>
       <c r="P27" s="243" t="inlineStr">
         <is>
-          <t>signalStatus</t>
+          <t>status</t>
         </is>
       </c>
       <c r="Q27" s="244" t="inlineStr"/>
@@ -4041,12 +4039,12 @@
       </c>
       <c r="O28" s="243" t="inlineStr">
         <is>
-          <t>app_early_warning_info</t>
+          <t>app_early_warning_signal_info</t>
         </is>
       </c>
       <c r="P28" s="243" t="inlineStr">
         <is>
-          <t>signalRiskLevel</t>
+          <t>warningLevel</t>
         </is>
       </c>
       <c r="Q28" s="244" t="inlineStr"/>
@@ -4092,12 +4090,12 @@
       </c>
       <c r="O29" s="243" t="inlineStr">
         <is>
-          <t>app_early_warning_info</t>
+          <t>app_early_warning_signal_info</t>
         </is>
       </c>
       <c r="P29" s="243" t="inlineStr">
         <is>
-          <t>signalCreateTime</t>
+          <t>inputDate</t>
         </is>
       </c>
       <c r="Q29" s="244" t="inlineStr"/>
@@ -4203,32 +4201,30 @@
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId};
 【3】提供数据：工商股东名称、股东持股数、股东出资金额
-    时点：最新（snapshot_type='latest'）
--- 源数据表：app_ic_shareholder_info（最新时点，snapshot_type='latest'）
-SELECT
-    a.icShareholderName AS 工商股东名称,
-    a.icStockNum AS 股东持股数,
-    a.icAmount AS 股东出资金额
-FROM app_ic_shareholder_info a
-WHERE a.reportNo = #{reportNo}
-  AND a.customerId = #{customerId}
-  AND a.snapshot_type = 'latest';
--- 授信时点：snapshot_type='atCredit'(授信时点快照)（快照条件，按需取对应时点数据）
-【4】提供数据：系统股东名称、系统股东持股数、系统股东出资金额、系统股东持股比例
-    时点：当前数据（含授信时窗口要素[最新；授信时]，该表无快照字段，授信时差异由规则引擎处理）
+    时点：当前最新（表无快照）
 -- 源数据表：app_shareholder_info
 SELECT
-    a.name AS 系统股东名称,
-    a.stock_num AS 系统股东持股数,
-    a.amount AS 系统股东出资金额,
-    a.stock_percent AS 系统股东持股比例
+    a.name AS 工商股东名称,
+    a.stock_num AS 股东持股数,
+    a.amount AS 股东出资金额
 FROM app_shareholder_info a
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId};
-【5】提供数据：股权变更时间、变更前持股比例、变更后持股比例
+【4】提供数据：系统股东名称、系统股东持股比例、系统股东出资金额
+    时点：当前最新（表无快照）
+-- 源数据表：app_xd_shareholder_info
+SELECT
+    a.name AS 系统股东名称,
+    a.investmentProp AS 系统股东持股比例,
+    a.oughtSum AS 系统股东出资金额
+FROM app_xd_shareholder_info a
+WHERE a.reportNo = #{reportNo}
+  AND a.customerId = #{customerId};
+【5】提供数据：股东名称、股权变更时间、变更前持股比例、变更后持股比例
     时点：授信时（snapshot_type='atCredit'）
 -- 源数据表：app_ic_shareholder_info（授信时时点，snapshot_type='atCredit'）
 SELECT
+    a.icShareholderName AS 股东名称_授信,
     a.changeTime AS 股权变更时间_授信,
     a.percentBefore AS 变更前持股比例_授信,
     a.percentAfter AS 变更后持股比例_授信
@@ -4236,17 +4232,22 @@
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId}
   AND a.snapshot_type = 'atCredit';
-【6】提供数据：股权变更时间、变更前持股比例、变更后持股比例
+【6】提供数据：股东名称、股权变更时间、变更前持股比例、变更后持股比例
     时点：最新（snapshot_type='latest'）
 -- 源数据表：app_ic_shareholder_info（最新时点，snapshot_type='latest'）
 SELECT
+    a.icShareholderName AS 股东名称_最新,
     a.changeTime AS 股权变更时间_最新,
     a.percentBefore AS 变更前持股比例_最新,
     a.percentAfter AS 变更后持股比例_最新
 FROM app_ic_shareholder_info a
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId}
-  AND a.snapshot_type = 'latest';</t>
+  AND a.snapshot_type = 'latest';
+【7】提供数据：授信时点
+    时点：—（元信息/入参说明，无需查询）
+-- 源数据表：app_ic_shareholder_info（本块为入参/口径说明，无需查询）
+-- 授信时点：snapshot_type='atCredit'(授信时点快照)（快照条件，按需取对应时点数据）</t>
         </is>
       </c>
     </row>
@@ -4342,12 +4343,12 @@
       </c>
       <c r="O32" s="253" t="inlineStr">
         <is>
-          <t>app_ic_shareholder_info</t>
+          <t>app_shareholder_info</t>
         </is>
       </c>
       <c r="P32" s="253" t="inlineStr">
         <is>
-          <t>icShareholderName</t>
+          <t>name</t>
         </is>
       </c>
       <c r="Q32" s="254" t="inlineStr"/>
@@ -4393,7 +4394,7 @@
       </c>
       <c r="O33" s="253" t="inlineStr">
         <is>
-          <t>app_shareholder_info</t>
+          <t>app_xd_shareholder_info</t>
         </is>
       </c>
       <c r="P33" s="253" t="inlineStr">
@@ -4444,12 +4445,12 @@
       </c>
       <c r="O34" s="253" t="inlineStr">
         <is>
-          <t>app_shareholder_info</t>
+          <t>app_ic_shareholder_info</t>
         </is>
       </c>
       <c r="P34" s="253" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>icShareholderName</t>
         </is>
       </c>
       <c r="Q34" s="254" t="inlineStr"/>
@@ -4699,12 +4700,12 @@
       </c>
       <c r="O39" s="253" t="inlineStr">
         <is>
-          <t>app_ic_shareholder_info</t>
+          <t>app_shareholder_info</t>
         </is>
       </c>
       <c r="P39" s="253" t="inlineStr">
         <is>
-          <t>icStockNum</t>
+          <t>stock_num</t>
         </is>
       </c>
       <c r="Q39" s="254" t="inlineStr"/>
@@ -4750,12 +4751,12 @@
       </c>
       <c r="O40" s="253" t="inlineStr">
         <is>
-          <t>app_ic_shareholder_info</t>
+          <t>app_shareholder_info</t>
         </is>
       </c>
       <c r="P40" s="253" t="inlineStr">
         <is>
-          <t>icAmount</t>
+          <t>amount</t>
         </is>
       </c>
       <c r="Q40" s="254" t="inlineStr"/>
@@ -4874,7 +4875,7 @@
       </c>
       <c r="O42" s="180" t="inlineStr">
         <is>
-          <t>app_shareholder_info</t>
+          <t>app_xd_shareholder_info</t>
         </is>
       </c>
       <c r="P42" s="180" t="inlineStr">
@@ -4885,16 +4886,24 @@
       <c r="Q42" s="181" t="inlineStr">
         <is>
           <t>-- 经验库规则判断所需源数据（二、客户基本情况，规则引擎自行判断命中逻辑）
-【1】提供数据：系统股东名称、股东假冒国企标签
+【1】提供数据：系统股东名称
     时点：当前最新（表无快照）
--- 源数据表：app_shareholder_info
+-- 源数据表：app_xd_shareholder_info
 SELECT
-    a.name AS 系统股东名称,
+    a.name AS 系统股东名称
+FROM app_xd_shareholder_info a
+WHERE a.reportNo = #{reportNo}
+  AND a.customerId = #{customerId};
+【2】提供数据：股东名称、股东假冒国企标签
+    时点：当前最新（表无快照）
+-- 源数据表：app_shareholder_info（工商股东最新，含假冒国企标签）
+SELECT
+    a.name AS 股东名称,
     a.is_fake_state_owned AS 股东假冒国企标签
 FROM app_shareholder_info a
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId};
-【2】提供数据：是否是假冒国企
+【3】提供数据：是否是假冒国企
     时点：当前最新（表无快照）
 -- 源数据表：app_customer_info
 SELECT
@@ -20851,19 +20860,25 @@
       </c>
       <c r="Q328" s="165" t="inlineStr">
         <is>
-          <t>-- 近一年预警任务（按发起时间倒序）
+          <t>-- 1) 近一年预警任务（按发起时间倒序）
 SELECT
     a.inputDate          AS 预警本次发起时间,
     a.approveStatusName  AS 审批状态,
     a.riskTaskType       AS 任务类型,
-    a.warnLevel          AS 客户风险等级,
-    a.riskReasonCount    AS 近一年每个风险原因数量,
-    a.riskReasonTodoCount AS 近一年每个风险原因待填写数量
+    a.warnLevel          AS 客户风险等级
 FROM app_early_warning_info a
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId}
   AND a.inputDate &gt;= DATE_FORMAT(DATE_SUB(NOW(), INTERVAL 1 YEAR), '%Y-%m-%d')
-ORDER BY a.inputDate DESC;</t>
+ORDER BY a.inputDate DESC;
+-- 2) 近一年预警信号数量（按风险原因分类，独立信号台账表）
+SELECT
+    a.riskMessage AS 风险原因,
+    a.count       AS 近一年每个风险原因数量,
+    a.readyCount  AS 近一年每个风险原因待填写数量
+FROM app_early_warning_signal_info a
+WHERE a.reportNo = #{reportNo}
+  AND a.customerId = #{customerId};</t>
         </is>
       </c>
     </row>
@@ -21041,12 +21056,12 @@
       <c r="N332" s="242" t="n"/>
       <c r="O332" s="243" t="inlineStr">
         <is>
-          <t>app_early_warning_info</t>
+          <t>app_early_warning_signal_info</t>
         </is>
       </c>
       <c r="P332" s="243" t="inlineStr">
         <is>
-          <t>riskReasonCount</t>
+          <t>count</t>
         </is>
       </c>
       <c r="Q332" s="244" t="inlineStr"/>
@@ -21084,12 +21099,12 @@
       <c r="N333" s="242" t="n"/>
       <c r="O333" s="243" t="inlineStr">
         <is>
-          <t>app_early_warning_info</t>
+          <t>app_early_warning_signal_info</t>
         </is>
       </c>
       <c r="P333" s="243" t="inlineStr">
         <is>
-          <t>riskReasonTodoCount</t>
+          <t>readyCount</t>
         </is>
       </c>
       <c r="Q333" s="244" t="inlineStr"/>
@@ -21179,7 +21194,7 @@
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId}
 ORDER BY a.confirmDate DESC;
--- 2) 他项权利/限制权利明细
+-- 2) 他项权利明细
 SELECT
     a.clrName             AS 关联押品名称,
     a.pledgeSerialNo      AS 不动产登记编号,
@@ -21188,10 +21203,15 @@
     a.pledgeTypeName      AS 抵押方式,
     a.maxCreditorAmt      AS 债权数额,
     a.startEnd            AS 债务履行期限,
-    a.registerTimestamp   AS 设定日期,
-    a.attachmentOrg       AS 限制权人,
-    a.attachmentTypeName  AS 查封类型
+    a.registerTimestamp   AS 设定日期
 FROM app_collateral_mortgage_info a
+WHERE a.reportNo = #{reportNo}
+  AND a.customerId = #{customerId};
+-- 3) 限制权利明细（限制权人/查封类型，独立限制权利表）
+SELECT
+    a.attachmentOrg      AS 限制权人,
+    a.attachmentTypeName AS 查封类型
+FROM app_collateral_restricted_right a
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId};</t>
         </is>
@@ -21657,7 +21677,7 @@
       <c r="N344" s="250" t="n"/>
       <c r="O344" s="253" t="inlineStr">
         <is>
-          <t>app_collateral_mortgage_info</t>
+          <t>app_collateral_restricted_right</t>
         </is>
       </c>
       <c r="P344" s="253" t="inlineStr">
@@ -21704,7 +21724,7 @@
       <c r="N345" s="250" t="n"/>
       <c r="O345" s="253" t="inlineStr">
         <is>
-          <t>app_collateral_mortgage_info</t>
+          <t>app_collateral_restricted_right</t>
         </is>
       </c>
       <c r="P345" s="253" t="inlineStr">
@@ -22509,7 +22529,7 @@
       </c>
       <c r="O360" s="195" t="inlineStr">
         <is>
-          <t>app_collateral_mortgage_info</t>
+          <t>app_collateral_restricted_right</t>
         </is>
       </c>
       <c r="P360" s="195" t="inlineStr">
@@ -22522,11 +22542,11 @@
           <t>-- 经验库规则判断所需源数据（十二、担保情况和潜在风险，规则引擎自行判断命中逻辑）
 【1】提供数据：限制权人、查封类型
     时点：当前最新（表无快照）
--- 源数据表：app_collateral_mortgage_info
+-- 源数据表：app_collateral_restricted_right
 SELECT
     a.attachmentOrg AS 限制权人,
     a.attachmentTypeName AS 查封类型
-FROM app_collateral_mortgage_info a
+FROM app_collateral_restricted_right a
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId};</t>
         </is>
@@ -22573,7 +22593,7 @@
       </c>
       <c r="O361" s="201" t="inlineStr">
         <is>
-          <t>app_collateral_mortgage_info</t>
+          <t>app_collateral_restricted_right</t>
         </is>
       </c>
       <c r="P361" s="201" t="inlineStr">

--- a/src/main/resources/sql/20260819/app层/数据映射细化V4.xlsx
+++ b/src/main/resources/sql/20260819/app层/数据映射细化V4.xlsx
@@ -16902,12 +16902,12 @@
       <c r="N260" s="232" t="n"/>
       <c r="O260" s="233" t="inlineStr">
         <is>
-          <t>app_credit_debt_detail</t>
+          <t>app_credit_report_info</t>
         </is>
       </c>
       <c r="P260" s="233" t="inlineStr">
         <is>
-          <t>加工:征信短借-财报短借</t>
+          <t>creditShortTermDiff</t>
         </is>
       </c>
       <c r="Q260" s="234" t="inlineStr"/>
@@ -16941,12 +16941,12 @@
       <c r="N261" s="232" t="n"/>
       <c r="O261" s="233" t="inlineStr">
         <is>
-          <t>app_credit_debt_detail</t>
+          <t>app_credit_report_info</t>
         </is>
       </c>
       <c r="P261" s="233" t="inlineStr">
         <is>
-          <t>加工:征信长借-财报长借(含一年内到期)</t>
+          <t>creditLongTermDiff</t>
         </is>
       </c>
       <c r="Q261" s="234" t="inlineStr"/>
@@ -17009,12 +17009,12 @@
       </c>
       <c r="O262" s="164" t="inlineStr">
         <is>
-          <t>app_credit_debt_detail</t>
+          <t>app_credit_report_info</t>
         </is>
       </c>
       <c r="P262" s="164" t="inlineStr">
         <is>
-          <t>加工:(征信债务-财报债务)/财报债务</t>
+          <t>creditDebtDeviation</t>
         </is>
       </c>
       <c r="Q262" s="165" t="inlineStr">
@@ -17103,7 +17103,7 @@
       </c>
       <c r="O263" s="171" t="inlineStr">
         <is>
-          <t>app_guarantor_credit_info</t>
+          <t>app_credit_report_info</t>
         </is>
       </c>
       <c r="P263" s="171" t="inlineStr">
@@ -17114,19 +17114,11 @@
       <c r="Q263" s="172" t="inlineStr">
         <is>
           <t>-- 经验库规则判断所需源数据（六、征信情况和潜在风险，规则引擎自行判断命中逻辑）
-【1】提供数据：在非银机构对外担保余额
-    时点：当前数据（含授信时窗口要素[最新；授信时]，该表无快照字段，授信时差异由规则引擎处理）
--- 源数据表：app_guarantor_credit_info
-SELECT
-    a.nonBankGuaranteeBal AS 在非银机构对外担保余额
-FROM app_guarantor_credit_info a
-WHERE a.reportNo = #{reportNo}
-  AND a.customerId = #{customerId}
-  AND a.queryTime = #{guarantorQueryTime};
-【2】提供数据：在非银机构负债合计
+【1】提供数据：在非银机构对外担保余额、在非银机构负债合计
     时点：当前数据（含授信时窗口要素[最新；授信时]，该表无快照字段，授信时差异由规则引擎处理）
 -- 源数据表：app_credit_report_info
 SELECT
+    a.nonBankGuaranteeBal AS 在非银机构对外担保余额,
     a.nonBankLiabTotal AS 在非银机构负债合计
 FROM app_credit_report_info a
 WHERE a.reportNo = #{reportNo}
@@ -17251,7 +17243,7 @@
       </c>
       <c r="P265" s="180" t="inlineStr">
         <is>
-          <t>bankLeaseOrgCount</t>
+          <t>loanBankOrgCount+guaranteeBankOrgCount(加工:企业借贷机构数+企业担保机构数合计)</t>
         </is>
       </c>
       <c r="Q265" s="181" t="inlineStr">
@@ -17261,11 +17253,12 @@
     时点：当前最新（表无快照）
 -- 源数据表：app_credit_report_info
 SELECT
-    a.bankLeaseOrgCount AS 合作银行及融资租赁机构数
+    a.loanBankOrgCount+guaranteeBankOrgCount AS 合作银行及融资租赁机构数
 FROM app_credit_report_info a
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId}
   AND a.queryTime = #{creditQueryTime};
+-- 合作银行及融资租赁机构数：加工:企业借贷机构数+企业担保机构数合计
 【2】提供数据：授信金额
     时点：当前最新（表无快照）
 -- 源数据表：app_specific_loan_check_info
@@ -24842,12 +24835,12 @@
       <c r="N404" s="215" t="n"/>
       <c r="O404" s="216" t="inlineStr">
         <is>
-          <t>app_credit_debt_detail</t>
+          <t>app_credit_report_info</t>
         </is>
       </c>
       <c r="P404" s="216" t="inlineStr">
         <is>
-          <t>加工:征信短借-财报短借</t>
+          <t>creditShortTermDiff</t>
         </is>
       </c>
       <c r="Q404" s="217" t="inlineStr"/>
@@ -24881,12 +24874,12 @@
       <c r="N405" s="215" t="n"/>
       <c r="O405" s="216" t="inlineStr">
         <is>
-          <t>app_credit_debt_detail</t>
+          <t>app_credit_report_info</t>
         </is>
       </c>
       <c r="P405" s="216" t="inlineStr">
         <is>
-          <t>加工:征信长借-财报长借(含一年内到期)</t>
+          <t>creditLongTermDiff</t>
         </is>
       </c>
       <c r="Q405" s="217" t="inlineStr"/>
@@ -26205,7 +26198,7 @@
       </c>
       <c r="O430" s="171" t="inlineStr">
         <is>
-          <t>app_guarantor_credit_info</t>
+          <t>app_credit_report_info</t>
         </is>
       </c>
       <c r="P430" s="171" t="inlineStr">
@@ -26218,14 +26211,14 @@
           <t>-- 经验库规则判断所需源数据（十二、担保情况和潜在风险，规则引擎自行判断命中逻辑）
 【1】提供数据：对外担保/净资产_最近一期（剔除我行业务）、对外担保（相关还款责任）余额（剔除我行）
     时点：当前数据（含授信时窗口要素[最新；授信时]，该表无快照字段，授信时差异由规则引擎处理）
--- 源数据表：app_guarantor_credit_info
+-- 源数据表：app_credit_report_info
 SELECT
     a.guaranteeNetAsset AS 对外担保/净资产_最近一期（剔除我行业务）,
     a.guaranteeBalanceExBank AS 对外担保（相关还款责任）余额（剔除我行）
-FROM app_guarantor_credit_info a
+FROM app_credit_report_info a
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId}
-  AND a.queryTime = #{guarantorQueryTime};</t>
+  AND a.queryTime = #{creditQueryTime};</t>
         </is>
       </c>
     </row>
@@ -26266,7 +26259,7 @@
       </c>
       <c r="O431" s="253" t="inlineStr">
         <is>
-          <t>app_guarantor_credit_info</t>
+          <t>app_credit_report_info</t>
         </is>
       </c>
       <c r="P431" s="253" t="inlineStr">
@@ -26351,24 +26344,16 @@
       <c r="Q432" s="181" t="inlineStr">
         <is>
           <t>-- 经验库规则判断所需源数据（十二、担保情况和潜在风险，规则引擎自行判断命中逻辑）
-【1】提供数据：在非银机构对外担保余额
+【1】提供数据：在非银机构对外担保余额、在非银机构负债合计
     时点：当前数据（含授信时窗口要素[最新；授信时]，该表无快照字段，授信时差异由规则引擎处理）
 -- 源数据表：app_guarantor_credit_info
 SELECT
-    a.nonBankGuaranteeBal AS 在非银机构对外担保余额
+    a.nonBankGuaranteeBal AS 在非银机构对外担保余额,
+    a.nonBankLiabTotal AS 在非银机构负债合计
 FROM app_guarantor_credit_info a
 WHERE a.reportNo = #{reportNo}
   AND a.customerId = #{customerId}
-  AND a.queryTime = #{guarantorQueryTime};
-【2】提供数据：在非银机构负债合计
-    时点：当前数据（含授信时窗口要素[最新；授信时]，该表无快照字段，授信时差异由规则引擎处理）
--- 源数据表：app_credit_report_info
-SELECT
-    a.nonBankLiabTotal AS 在非银机构负债合计
-FROM app_credit_report_info a
-WHERE a.reportNo = #{reportNo}
-  AND a.customerId = #{customerId}
-  AND a.queryTime = #{creditQueryTime};</t>
+  AND a.queryTime = #{guarantorQueryTime};</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26394,7 @@
       </c>
       <c r="O433" s="186" t="inlineStr">
         <is>
-          <t>app_credit_report_info</t>
+          <t>app_guarantor_credit_info</t>
         </is>
       </c>
       <c r="P433" s="186" t="inlineStr">
